--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/coassignment_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/coassignment_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,960 +436,824 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
+          <t>DR-157</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.9405144694533762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9891975308641975</v>
+        <v>0.5879478827361564</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.9262295081967213</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5588673621460507</v>
+        <v>0.004830917874396135</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.9042207792207793</v>
       </c>
       <c r="J2" t="n">
-        <v>0.540625</v>
+        <v>0.9477977161500816</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.9248366013071896</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.01597444089456869</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8996865203761756</v>
+        <v>0.004777070063694267</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9392523364485982</v>
+        <v>0.01794453507340946</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5395348837209303</v>
+        <v>0.8667736757624398</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4204018547140649</v>
+        <v>0.03392568659127625</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.01970443349753695</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5869218500797448</v>
+        <v>0.8865478119935171</v>
       </c>
       <c r="T2" t="n">
-        <v>0.984375</v>
+        <v>0.01857585139318885</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9846860643185299</v>
+        <v>0.9448698315467075</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.01410658307210031</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5023183925811437</v>
+        <v>0.01762820512820513</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5796875</v>
+        <v>0.342443729903537</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6835637480798771</v>
+        <v>0.5758064516129032</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8790697674418605</v>
+        <v>0.8916666666666667</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5496794871794872</v>
+        <v>0.4151260504201681</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5507936507936508</v>
+        <v>0.8801261829652997</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4621578099838969</v>
+        <v>0.09531249999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5541795665634675</v>
+        <v>0.8507223113964687</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5536547433903577</v>
+        <v>0.1540930979133226</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5634674922600619</v>
+        <v>0.02131147540983606</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.546969696969697</v>
+        <v>0.02283849918433932</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1959564541213064</v>
+        <v>0.1893203883495146</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5461658841940532</v>
+        <v>0.6841243862520459</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.5632911392405063</v>
+        <v>0.03179650238473768</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5273010920436817</v>
+        <v>0.8622366288492707</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8208269525267994</v>
+        <v>0.4790322580645161</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5799701046337817</v>
+        <v>0.9207119741100324</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9721362229102167</v>
+        <v>0.930976430976431</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1812688821752266</v>
+        <v>0.8717532467532467</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4024960998439938</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.05405405405405406</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.5276073619631901</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.6037441497659907</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.6213292117465224</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.2339089481946625</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.512937595129376</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.5300632911392406</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
+        <v>0.4501607717041801</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.9405144694533762</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.5293159609120521</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.8347245409015025</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.8786407766990292</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.8298217179902755</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.0592</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.009646302250803859</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.9612277867528272</v>
       </c>
       <c r="P3" t="n">
-        <v>0.984</v>
+        <v>0.2971246006389776</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007874015748031496</v>
+        <v>0.09309791332263243</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.9622331691297209</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.07290015847860538</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.8456883509833586</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0.07313195548489666</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003174603174603175</v>
+        <v>0.06698564593301436</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3420195439739414</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.5314009661835749</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.9900332225913622</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.5058823529411764</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.8006279434850864</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.1589825119236884</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.9483870967741935</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.2512</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.08745874587458746</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.07467532467532467</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2088607594936709</v>
+        <v>0.2790322580645161</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.6270903010033445</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.08842443729903537</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.7915993537964459</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.5668789808917197</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.8516129032258064</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.8462809917355372</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2419601837672282</v>
+        <v>0.7990196078431373</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.009433962264150943</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.4040561622464899</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.2057877813504823</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.003144654088050315</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.4878048780487805</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9891975308641975</v>
+        <v>0.5879478827361564</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.5293159609120521</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9984472049689441</v>
+        <v>0.2990033222591362</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.3431542461005199</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.6512396694214876</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4946889226100152</v>
+        <v>0.3617021276595745</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.6605960264900662</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4826498422712934</v>
+        <v>0.6429752066115703</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.6606260296540363</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.001655629139072848</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9061032863849765</v>
+        <v>0.2977346278317152</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9587301587301588</v>
+        <v>0.001703577512776831</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4737654320987654</v>
+        <v>0.4448051948051948</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1050080775444265</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3697996918335901</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.001683501683501683</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6463022508038585</v>
+        <v>0.4730831973898858</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.0016</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0.6462264150943396</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.554160125588697</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5165876777251185</v>
+        <v>0.2108731466227348</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7268445839874411</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8522012578616353</v>
+        <v>0.4906303236797274</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4840255591054313</v>
+        <v>0.2033898305084746</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5</v>
+        <v>0.6916932907348243</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4085850556438791</v>
+        <v>0.03833865814696485</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4930448222565688</v>
+        <v>0.4457236842105263</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4921630094043887</v>
+        <v>0.06991869918699187</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5101404056162246</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4818181818181818</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.2294573643410853</v>
+        <v>0.09461663947797716</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4889589905362776</v>
+        <v>0.5083612040133779</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.4952380952380953</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.482442748091603</v>
+        <v>0.8665594855305466</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.7921875</v>
+        <v>0.2508196721311475</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5030120481927711</v>
+        <v>0.6445182724252492</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9875</v>
+        <v>0.6512820512820513</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2187981510015408</v>
+        <v>0.6254180602006689</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.344391785150079</v>
+        <v>0.5360134003350083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.07121212121212121</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.463302752293578</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.6565977742448331</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.6537267080745341</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.2795527156549521</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.5632716049382716</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.9779527559055118</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.4673046251993621</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.9907834101382489</v>
+        <v>0.2406504065040651</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9984472049689441</v>
+        <v>0.2990033222591362</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5199386503067485</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.001644736842105263</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5063291139240507</v>
+        <v>0.003344481605351171</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.001661129568106312</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.03583061889250815</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8992</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.946031746031746</v>
+        <v>0.02504173622704508</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5093457943925234</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.004983388704318937</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3830455259026688</v>
+        <v>0.02454991816693944</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.03247863247863248</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6284779050736498</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9968354430379747</v>
+        <v>0.032</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9953703703703703</v>
+        <v>0.001584786053882726</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.033003300330033</v>
       </c>
       <c r="W5" t="n">
-        <v>0.539308176100629</v>
+        <v>0.03150912106135987</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5445859872611465</v>
+        <v>0.006611570247933884</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7169811320754716</v>
+        <v>0.3222591362126246</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8665620094191523</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5149006622516556</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5211726384364821</v>
+        <v>0.001612903225806452</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4267100977198697</v>
+        <v>0.01437699680511182</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5197472353870458</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5173501577287066</v>
+        <v>0.009584664536741214</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5347758887171561</v>
+        <v>0.02302631578947368</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5054432348367029</v>
+        <v>0.01845637583892618</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2110236220472441</v>
+        <v>0.006525285481239805</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.5205696202531646</v>
+        <v>0.005</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.522508038585209</v>
+        <v>0.021630615640599</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5038520801232665</v>
+        <v>0.03119868637110016</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.785824345146379</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5398496240601504</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9813084112149533</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2067901234567901</v>
+        <v>0.001631321370309951</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.3700159489633174</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.06727828746177369</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.4916030534351145</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.6483870967741936</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.6392405063291139</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.2576489533011272</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.5383411580594679</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.5007849293563579</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1</v>
+        <v>0.003333333333333334</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.3431542461005199</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9412698412698413</v>
+        <v>0.008635578583765112</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.98145285935085</v>
+        <v>0.02188552188552189</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.01164725457570715</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9414556962025317</v>
+        <v>0.009950248756218905</v>
       </c>
       <c r="L6" t="n">
-        <v>0.955177743431221</v>
+        <v>0.001703577512776831</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.8483333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004702194357366771</v>
+        <v>0.003389830508474576</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9508716323296355</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0108359133126935</v>
+        <v>0.001672240802675585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9319620253164557</v>
+        <v>0.003430531732418525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03662420382165605</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.003231017770597738</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.008025682182985553</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9355828220858896</v>
+        <v>0.003355704697986577</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0515625</v>
+        <v>0.001677852348993289</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.001675041876046901</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01713395638629283</v>
+        <v>0.3560975609756097</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1398,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>0.02117263843648208</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001592356687898089</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1410,4086 +1274,3462 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.001677852348993289</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.001689189189189189</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.3092621664050236</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>0.00684931506849315</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.00165016501650165</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>0.07154471544715447</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>0.008361204013377926</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>0.008710801393728223</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.3440366972477064</v>
+        <v>0.006666666666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.01095461658841941</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.5225903614457831</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.04081632653061224</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.02773497688751926</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.3023622047244094</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.04923076923076923</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.9262295081967213</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.8347245409015025</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.6512396694214876</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9412698412698413</v>
+        <v>0.008635578583765112</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.008278145695364239</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.9650582362728786</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.02013422818791946</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.008090614886731391</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.02249134948096886</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.7330016583747927</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9902597402597403</v>
+        <v>0.1747572815533981</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004754358161648178</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0.0136986301369863</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.7559322033898305</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0192</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.9968253968253968</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0.01626016260162602</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003184713375796179</v>
+        <v>0.01983471074380165</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3421487603305785</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.6437908496732027</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>0.7658119658119659</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.3407534246575342</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.9373996789727127</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.07049180327868852</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>0.714759535655058</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>0.1284552845528455</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.01487603305785124</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.01535836177474403</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.226537216828479</v>
+        <v>0.1523500810372772</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.02131147540983606</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>0.9237147595356551</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>0.3947797716150082</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.271875</v>
+        <v>0.9481605351170569</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0046875</v>
+        <v>0.8644628099173554</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.4234930448222566</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.2256</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
+        <v>0.4210526315789473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5588673621460507</v>
+        <v>0.004830917874396135</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4946889226100152</v>
+        <v>0.3617021276595745</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5199386503067485</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.008278145695364239</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.02917341977309562</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.01465798045602606</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.01143790849673203</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.01305057096247961</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5898617511520737</v>
+        <v>0.8314424635332253</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5030395136778115</v>
+        <v>0.008264462809917356</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8839285714285714</v>
+        <v>0.008143322475570033</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.0132013201320132</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1326053042121685</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4809160305343512</v>
+        <v>0.01105845181674566</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4556390977443609</v>
+        <v>0.009478672985781991</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.008130081300813009</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.01118210862619808</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9891640866873065</v>
+        <v>0.001636661211129296</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2597597597597597</v>
+        <v>0.3425774877650897</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7331288343558282</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0.02852614896988907</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.9229559748427673</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0.00975609756097561</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0.008223684210526315</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0060790273556231</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0.006493506493506494</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0.07085346215780998</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.7937219730941704</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.9779411764705882</v>
+        <v>0.008223684210526315</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.5468277945619335</v>
+        <v>0.008517887563884156</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002962962962962963</v>
+        <v>0.01140065146579805</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.8495440729483282</v>
+        <v>0.001658374792703151</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002928257686676428</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.1640625</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.1603053435114504</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.003076923076923077</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.081203007518797</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.5987558320373251</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.546969696969697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.9042207792207793</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.6605960264900662</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.001644736842105263</v>
       </c>
       <c r="F9" t="n">
-        <v>0.98145285935085</v>
+        <v>0.02188552188552189</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.02917341977309562</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9313725490196079</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.9756493506493507</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.04094488188976378</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.03184713375796178</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.04333333333333333</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.733652312599681</v>
       </c>
       <c r="P9" t="n">
-        <v>0.985981308411215</v>
+        <v>0.2006472491909385</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.006269592476489028</v>
+        <v>0.0448</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0.03801652892561983</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.7414075286415712</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0390015600624025</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.9721792890262752</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0.03525641025641026</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.03674121405750799</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4159869494290375</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.6376811594202898</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.3506711409395973</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.9354330708661417</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.709470304975923</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.1492776886035313</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.03074433656957929</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.03459637561779242</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.2062992125984252</v>
+        <v>0.1693290734824281</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>0.7761437908496732</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.03583061889250815</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>0.9145161290322581</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>0.4084967320261438</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>0.970873786407767</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>0.9697478991596639</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.2469512195121951</v>
+        <v>0.9690048939641109</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.004724409448818898</v>
+        <v>0.8441127694859039</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.4009146341463415</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.2135007849293564</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.003091190108191654</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
+        <v>0.4500818330605565</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.540625</v>
+        <v>0.9477977161500816</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.8786407766990292</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4826498422712934</v>
+        <v>0.6429752066115703</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5063291139240507</v>
+        <v>0.003344481605351171</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.01164725457570715</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.9650582362728786</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.01465798045602606</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.9313725490196079</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.9660743134087237</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5814696485623003</v>
+        <v>0.00326797385620915</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4976</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.778675282714055</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1558872305140962</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8880248833592534</v>
+        <v>0.003246753246753247</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.7903494176372712</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4651898734177215</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4400630914826498</v>
+        <v>0.978328173374613</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.107981220657277</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9855769230769231</v>
+        <v>0.3185550082101806</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.6310679611650486</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.8094435075885329</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0.3235800344234079</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9189627228525121</v>
+        <v>0.05475040257648953</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0.7655737704918033</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.116504854368932</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0.001658374792703151</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0.003316749585406302</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.007898894154818325</v>
+        <v>0.1373182552504039</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0.7074380165289256</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>0.9311475409836065</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.7515625</v>
+        <v>0.3944353518821604</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.9758308157099698</v>
+        <v>0.9656862745098039</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.5203761755485894</v>
+        <v>0.9699499165275459</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.003110419906687403</v>
+        <v>0.9024793388429752</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.8486312399355878</v>
+        <v>0.9003378378378378</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0045662100456621</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.14170692431562</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.1403508771929824</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.003225806451612903</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.06487341772151899</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.579454253611557</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.5337519623233909</v>
+        <v>0.3937397034596375</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.9248366013071896</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.8298217179902755</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.6606260296540363</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.001661129568106312</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9414556962025317</v>
+        <v>0.009950248756218905</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.01143790849673203</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9756493506493507</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.9660743134087237</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.0264026402640264</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.7263843648208469</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001607717041800643</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0.02192242833052277</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.7446808510638298</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.02870813397129187</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.9984301412872841</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0.02261712439418417</v>
       </c>
       <c r="W11" t="n">
-        <v>0.003184713375796179</v>
+        <v>0.02454991816693944</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3609271523178808</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.6519607843137255</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>0.3446519524617996</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>0.9287974683544303</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>0.08103727714748785</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.7100494233937397</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.01963993453355155</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.02635914332784185</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2256493506493507</v>
+        <v>0.1650326797385621</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>0.7651006711409396</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.03262642740619902</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>0.9118589743589743</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>0.4022617124394184</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.2531055900621118</v>
+        <v>0.9490131578947368</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.008</v>
+        <v>0.8647746243739566</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.3800623052959501</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.2171052631578947</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.004777070063694267</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
+        <v>0.4274193548387097</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.01597444089456869</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.0592</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.001655629139072848</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03583061889250815</v>
       </c>
       <c r="F12" t="n">
-        <v>0.955177743431221</v>
+        <v>0.001703577512776831</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.02013422818791946</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.01305057096247961</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.04094488188976378</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.0264026402640264</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.1805337519623234</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.1277955271565495</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0.7626016260162601</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001567398119122257</v>
+        <v>0.9795597484276729</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.1216</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.007704160246533128</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003125</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.6366559485530546</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>0.0957983193277311</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.5733558178752108</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.03993610223642172</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.8128</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.9884678747940692</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.9851973684210527</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1984251968503937</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>0.2630718954248366</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.9802955665024631</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>0.505654281098546</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>0.02597402597402598</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>0.01712328767123288</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.2386018237082067</v>
+        <v>0.07479674796747968</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.03908794788273615</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.3816793893129771</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.001524390243902439</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
+        <v>0.5390879478827362</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8996865203761756</v>
+        <v>0.004777070063694267</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.009646302250803859</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9061032863849765</v>
+        <v>0.2977346278317152</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8992</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.8483333333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.008090614886731391</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5898617511520737</v>
+        <v>0.8314424635332253</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.03184713375796178</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5814696485623003</v>
+        <v>0.00326797385620915</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.1805337519623234</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.1636952998379254</v>
       </c>
       <c r="O13" t="n">
-        <v>0.562111801242236</v>
+        <v>0.01895734597156398</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.1148325358851675</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4339035769828927</v>
+        <v>0.1616</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.1923714759535655</v>
       </c>
       <c r="S13" t="n">
-        <v>0.560064935064935</v>
+        <v>0.01779935275080906</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9137931034482759</v>
+        <v>0.1852433281004709</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9221183800623053</v>
+        <v>0.009104704097116844</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1860095389507154</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4992125984251968</v>
+        <v>0.1964856230031949</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6129541864139021</v>
+        <v>0.09149277688603531</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7126984126984127</v>
+        <v>0.2852512155591572</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.8</v>
+        <v>0.02124183006535948</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5737704918032787</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5888888888888889</v>
+        <v>0.021671826625387</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.1283676703645008</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.0211038961038961</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5841269841269842</v>
+        <v>0.1050955414012739</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.5984375</v>
+        <v>0.1578099838969404</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.577639751552795</v>
+        <v>0.1631663974151858</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1752411575562701</v>
+        <v>0.1098726114649682</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.0593900481540931</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.593192868719611</v>
+        <v>0.1647819063004846</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.5739268680445151</v>
+        <v>0.03503184713375796</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.7456828885400314</v>
+        <v>0.0593900481540931</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.6018376722817764</v>
+        <v>0.01116427432216906</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.8785488958990536</v>
+        <v>0.009917355371900827</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.1679506933744222</v>
+        <v>0.01607717041800643</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.004893964110929853</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.05513016845329249</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.5595054095826894</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.5784469096671949</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.5921259842519685</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.2188498402555911</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.4758942457231726</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.8944805194805194</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.5629032258064516</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0.8918495297805643</v>
+        <v>0.07740916271721959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9392523364485982</v>
+        <v>0.01794453507340946</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9587301587301588</v>
+        <v>0.001703577512776831</v>
       </c>
       <c r="E14" t="n">
-        <v>0.946031746031746</v>
+        <v>0.02504173622704508</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004702194357366771</v>
+        <v>0.003389830508474576</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.02249134948096886</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5030395136778115</v>
+        <v>0.008264462809917356</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.04333333333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4976</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.1636952998379254</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4866562009419153</v>
+        <v>0.1655737704918033</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.7742998352553542</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3543307086614173</v>
+        <v>0.9816360601001669</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6479099678456591</v>
+        <v>0.1488294314381271</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9619651347068146</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9856687898089171</v>
+        <v>0.007911392405063292</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5658307210031348</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.7507936507936508</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.7914012738853503</v>
+        <v>0.1254295532646048</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.5976027397260274</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5048543689320388</v>
+        <v>0.03420195439739414</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4059900166389351</v>
+        <v>0.8967741935483871</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5023622047244094</v>
+        <v>0.1822742474916388</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.5047318611987381</v>
+        <v>0.8377049180327869</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.5164319248826291</v>
+        <v>0.9884105960264901</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.4984177215189873</v>
+        <v>0.9833055091819699</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.22508038585209</v>
+        <v>0.803921568627451</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.5087719298245614</v>
+        <v>0.2716666666666667</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.5111464968152867</v>
+        <v>0.9833887043189369</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.4960998439937597</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.7364341085271318</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5251141552511416</v>
+        <v>0.02675585284280936</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.931637519872814</v>
+        <v>0.01727115716753022</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.2186046511627907</v>
+        <v>0.08263069139966273</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.3574803149606299</v>
+        <v>0.05084745762711865</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.06955177743431221</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.4721362229102167</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0.6495176848874598</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.6687797147385103</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.2688</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.5467289719626168</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.9216965742251223</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0.4719101123595505</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.5522388059701493</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5395348837209303</v>
+        <v>0.8667736757624398</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.9612277867528272</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4737654320987654</v>
+        <v>0.4448051948051948</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5093457943925234</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.7330016583747927</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.733652312599681</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.778675282714055</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.7263843648208469</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1277955271565495</v>
       </c>
       <c r="M15" t="n">
-        <v>0.562111801242236</v>
+        <v>0.01895734597156398</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4866562009419153</v>
+        <v>0.1655737704918033</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.3912337662337662</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8921417565485362</v>
+        <v>0.1887096774193548</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1255961844197138</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.456386292834891</v>
+        <v>0.1580594679186229</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4327666151468315</v>
+        <v>0.7538699690402477</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1568938193343899</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1069767441860465</v>
+        <v>0.1421647819063005</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9857142857142858</v>
+        <v>0.3824959481361426</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2453416149068323</v>
+        <v>0.4392220421393841</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7203125</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0.6183986371379898</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0.7131410256410257</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9234449760765551</v>
+        <v>0.2614896988906498</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>0.3549920760697306</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0.1821138211382114</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.1565074135090609</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.004694835680751174</v>
+        <v>0.3776337115072934</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0.589018302828619</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>0.180354267310789</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>0.6781045751633987</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.7538940809968847</v>
+        <v>0.6699029126213593</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.9759398496240601</v>
+        <v>0.7577235772357723</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.5162287480680062</v>
+        <v>0.7495854063018242</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.7198697068403909</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.8520249221183801</v>
+        <v>0.9618573797678275</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.004497751124437781</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.1489698890649762</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.1419656786271451</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.001584786053882726</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.07526881720430108</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.5707547169811321</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.5349922239502333</v>
+        <v>0.5926517571884984</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="C16" t="n">
-        <v>0.984</v>
+        <v>0.2971246006389776</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.1050080775444265</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.004983388704318937</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9508716323296355</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9902597402597403</v>
+        <v>0.1747572815533981</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.985981308411215</v>
+        <v>0.2006472491909385</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.1558872305140962</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0.7626016260162601</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.1148325358851675</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.7742998352553542</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.3912337662337662</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0192</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>0.982200647249191</v>
+        <v>0.7549668874172185</v>
       </c>
       <c r="S16" t="n">
-        <v>0.00487012987012987</v>
+        <v>0.400974025974026</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.7765625</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.1784615384615384</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9828926905132193</v>
+        <v>0.7697262479871175</v>
       </c>
       <c r="W16" t="n">
-        <v>0.004769475357710651</v>
+        <v>0.7870662460567823</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>0.1046698872785829</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>0.391156462585034</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>0.8569023569023569</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.2173228346456693</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.003294892915980231</v>
+        <v>0.9561815336463224</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.4228934817170111</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.9701726844583988</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.7688603531300161</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.7974068071312804</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.2676056338028169</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>0.351575456053068</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.8414239482200647</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>0.1626794258373206</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>0.8464</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.1872964169381107</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>0.1644518272425249</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.2993827160493827</v>
+        <v>0.2234910277324633</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0208</v>
+        <v>0.2915980230642504</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.4837209302325581</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.001610305958132045</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0.2599681020733652</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.01257861635220126</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
+        <v>0.7887096774193548</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4204018547140649</v>
+        <v>0.03392568659127625</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007874015748031496</v>
+        <v>0.09309791332263243</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3697996918335901</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3830455259026688</v>
+        <v>0.02454991816693944</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0108359133126935</v>
+        <v>0.001672240802675585</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004754358161648178</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8839285714285714</v>
+        <v>0.008143322475570033</v>
       </c>
       <c r="I17" t="n">
-        <v>0.006269592476489028</v>
+        <v>0.0448</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8880248833592534</v>
+        <v>0.003246753246753247</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001607717041800643</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001567398119122257</v>
+        <v>0.9795597484276729</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4339035769828927</v>
+        <v>0.1616</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3543307086614173</v>
+        <v>0.9816360601001669</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8921417565485362</v>
+        <v>0.1887096774193548</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0192</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.9819376026272578</v>
       </c>
       <c r="S17" t="n">
-        <v>0.04952076677316294</v>
+        <v>0.1699346405228758</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3369397217928903</v>
+        <v>0.9795597484276729</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3260530421216848</v>
+        <v>0.01232665639445301</v>
       </c>
       <c r="V17" t="n">
-        <v>0.007633587786259542</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04813664596273292</v>
+        <v>0.9773462783171522</v>
       </c>
       <c r="X17" t="n">
-        <v>0.875</v>
+        <v>0.6546644844517185</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1411042944785276</v>
+        <v>0.004807692307692308</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.5935085007727975</v>
+        <v>0.1531986531986532</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.89171974522293</v>
+        <v>0.635</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8808373590982287</v>
+        <v>0.05520504731861198</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.9278846153846154</v>
+        <v>0.904</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8755760368663594</v>
+        <v>0.2012882447665056</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.8761609907120743</v>
+        <v>0.8194888178913738</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.8728682170542635</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.8931297709923665</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1133858267716535</v>
+        <v>0.8066561014263075</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.8757861635220126</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.8770226537216829</v>
+        <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.9003115264797508</v>
+        <v>0.006504065040650406</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.6191950464396285</v>
+        <v>0.5756097560975609</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.8649468892261002</v>
+        <v>0.03064516129032258</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.3946957878315133</v>
+        <v>0.01830282861896839</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.09021406727828746</v>
+        <v>0.08674304418985269</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0.0755336617405583</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.1291793313069909</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.9041731066460588</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.05405405405405406</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.05817610062893082</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.06847133757961783</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.04482225656877898</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.4528</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.903125</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0.4101382488479263</v>
+        <v>0.5829307568438004</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.01970443349753695</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.001683501683501683</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.03247863247863248</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9319620253164557</v>
+        <v>0.003430531732418525</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0.0136986301369863</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.0132013201320132</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.03801652892561983</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.02192242833052277</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.1923714759535655</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="P18" t="n">
-        <v>0.982200647249191</v>
+        <v>0.7549668874172185</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.9819376026272578</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.1383333333333333</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.004746835443037975</v>
       </c>
       <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.003179650238473768</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6336134453781512</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>0.1179487179487179</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.0420032310177706</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.8926829268292683</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.1616666666666667</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.8105436573311368</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.9916805324459235</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.984873949579832</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.2122186495176849</v>
+        <v>0.7859531772575251</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>0.2789915966386555</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.9849498327759197</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>0.4941763727121464</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>0.02030456852791878</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>0.0155440414507772</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.2453416149068323</v>
+        <v>0.07321131447587355</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.003231017770597738</v>
+        <v>0.04599659284497445</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.4104938271604938</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.2088091353996737</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.003149606299212598</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.5082781456953642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5869218500797448</v>
+        <v>0.8865478119935171</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.9622331691297209</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6463022508038585</v>
+        <v>0.4730831973898858</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6284779050736498</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03662420382165605</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.7559322033898305</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1326053042121685</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.7414075286415712</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.7903494176372712</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.7446808510638298</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1216</v>
       </c>
       <c r="M19" t="n">
-        <v>0.560064935064935</v>
+        <v>0.01779935275080906</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6479099678456591</v>
+        <v>0.1488294314381271</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1255961844197138</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.00487012987012987</v>
+        <v>0.400974025974026</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.04952076677316294</v>
+        <v>0.1699346405228758</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.1383333333333333</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6672025723472669</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6869009584664537</v>
+        <v>0.7732919254658385</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1375404530744337</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0.1309328968903437</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1456</v>
+        <v>0.4127243066884176</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.9318541996830428</v>
+        <v>0.4730831973898858</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.4283387622149837</v>
+        <v>0.9966159052453468</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1247947454844007</v>
+        <v>0.6520979020979021</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.140983606557377</v>
+        <v>0.7364217252396166</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1185308848080134</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1291866028708134</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.1405492730210016</v>
+        <v>0.3414239482200647</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1376</v>
+        <v>0.1586776859504132</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.126984126984127</v>
+        <v>0.1442786069651741</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.5957792207792207</v>
+        <v>0.3782894736842105</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.1314935064935065</v>
+        <v>0.5896147403685092</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1407766990291262</v>
+        <v>0.1639344262295082</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.1171749598715891</v>
+        <v>0.6941747572815534</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.3909531502423264</v>
+        <v>0.7051282051282052</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.15600624024961</v>
+        <v>0.7696078431372549</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.617741935483871</v>
+        <v>0.757679180887372</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5625990491283677</v>
+        <v>0.7245901639344262</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.0707395498392283</v>
+        <v>0.9681742043551089</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.391304347826087</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.1175523349436393</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.9983870967741936</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.6351791530944625</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.9765258215962441</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0.1201923076923077</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0.592948717948718</v>
+        <v>0.5880398671096345</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.984375</v>
+        <v>0.01857585139318885</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.07290015847860538</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.0016</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9968354430379747</v>
+        <v>0.032</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.003231017770597738</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0192</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4809160305343512</v>
+        <v>0.01105845181674566</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.0390015600624025</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4651898734177215</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.02870813397129187</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9137931034482759</v>
+        <v>0.1852433281004709</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9619651347068146</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.456386292834891</v>
+        <v>0.1580594679186229</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.7765625</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3369397217928903</v>
+        <v>0.9795597484276729</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6672025723472669</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0.007473841554559043</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4992050874403816</v>
+        <v>0.6523125996810207</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.7543035993740219</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.8362204724409449</v>
+        <v>0.116504854368932</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.4724919093851133</v>
+        <v>0.5799676898222941</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4856687898089172</v>
+        <v>0.04134762633996937</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3938906752411576</v>
+        <v>0.891271056661562</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.4744976816074188</v>
+        <v>0.1669266770670827</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.478806907378336</v>
+        <v>0.8248062015503876</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.490625</v>
+        <v>0.9889589905362776</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.4668721109399075</v>
+        <v>0.9841521394611727</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.2340764331210191</v>
+        <v>0.7996870109546166</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.4755905511811024</v>
+        <v>0.2736</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.4895666131621188</v>
+        <v>0.9811320754716981</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.4564183835182251</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.7695924764890282</v>
+        <v>0.5179407176287052</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5037707390648567</v>
+        <v>0.02531645569620253</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.9857594936708861</v>
+        <v>0.01470588235294118</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.2321981424148607</v>
+        <v>0.07448494453248812</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.3191823899371069</v>
+        <v>0.04846526655896607</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.0776255707762557</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.4567901234567901</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.6714743589743589</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.6807511737089202</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.2921348314606741</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0.5887850467289719</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.9712918660287081</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0.4578696343402226</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0.9861111111111112</v>
+        <v>0.5293185419968305</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9846860643185299</v>
+        <v>0.9448698315467075</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.8456883509833586</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.6462264150943396</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9953703703703703</v>
+        <v>0.001584786053882726</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.008025682182985553</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.9968253968253968</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4556390977443609</v>
+        <v>0.009478672985781991</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.9721792890262752</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4400630914826498</v>
+        <v>0.978328173374613</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.9984301412872841</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.007704160246533128</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9221183800623053</v>
+        <v>0.009104704097116844</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9856687898089171</v>
+        <v>0.007911392405063292</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4327666151468315</v>
+        <v>0.7538699690402477</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.1784615384615384</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3260530421216848</v>
+        <v>0.01232665639445301</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.004746835443037975</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6869009584664537</v>
+        <v>0.7732919254658385</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.007473841554559043</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.006134969325153374</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5953125</v>
+        <v>0.009160305343511451</v>
       </c>
       <c r="X21" t="n">
-        <v>0.478806907378336</v>
+        <v>0.3616692426584235</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.6460587326120556</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.8306962025316456</v>
+        <v>0.7835218093699515</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.4453376205787781</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4601910828025478</v>
+        <v>0.953030303030303</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.3608414239482201</v>
+        <v>0.07174887892376682</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.4468412942989214</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.4494556765163297</v>
+        <v>0.1305007587253414</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.4661538461538461</v>
+        <v>0.0046875</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.434984520123839</v>
+        <v>0.00949367088607595</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.23950233281493</v>
+        <v>0.1533742331288344</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.4544025157232705</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.4582677165354331</v>
+        <v>0.01246105919003115</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.4303599374021909</v>
+        <v>0.9342507645259939</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.7565485362095532</v>
+        <v>0.4083204930662558</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.481371087928465</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.9829192546583851</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.2367223065250379</v>
+        <v>0.942457231726283</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.3150470219435736</v>
+        <v>0.878740157480315</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.0791476407914764</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.4296636085626911</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.6915739268680445</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0.699685534591195</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.2952380952380952</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.5990712074303406</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.9682034976152624</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0.4272151898734177</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0.9815100154083205</v>
+        <v>0.4332298136645963</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.01410658307210031</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.07313195548489666</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.033003300330033</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9355828220858896</v>
+        <v>0.003355704697986577</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.01626016260162602</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.008130081300813009</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.03525641025641026</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.02261712439418417</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.1860095389507154</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.1568938193343899</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9828926905132193</v>
+        <v>0.7697262479871175</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.007633587786259542</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.1375404530744337</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.006134969325153374</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.003081664098613251</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.645933014354067</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>0.1191275167785235</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.5793918918918919</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>0.03616352201257862</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>0.8952380952380953</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.1677316293929713</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>0.8214849921011058</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>0.9934640522875817</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.9887820512820513</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.2232558139534884</v>
+        <v>0.797427652733119</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>0.2615894039735099</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.9838969404186796</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>0.5143769968051118</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.0207667731629393</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>0.009819967266775777</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.2564491654021244</v>
+        <v>0.07779578606158834</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.004651162790697674</v>
+        <v>0.04942339373970346</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.4170403587443946</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0.2125984251968504</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0.00302571860816944</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
+        <v>0.5237315875613748</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5023183925811437</v>
+        <v>0.01762820512820513</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003174603174603175</v>
+        <v>0.06698564593301436</v>
       </c>
       <c r="D23" t="n">
-        <v>0.554160125588697</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="E23" t="n">
-        <v>0.539308176100629</v>
+        <v>0.03150912106135987</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0515625</v>
+        <v>0.001677852348993289</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003184713375796179</v>
+        <v>0.01983471074380165</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.01118210862619808</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.03674121405750799</v>
       </c>
       <c r="J23" t="n">
-        <v>0.107981220657277</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.003184713375796179</v>
+        <v>0.02454991816693944</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003125</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4992125984251968</v>
+        <v>0.1964856230031949</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5658307210031348</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1069767441860465</v>
+        <v>0.1421647819063005</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004769475357710651</v>
+        <v>0.7870662460567823</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.04813664596273292</v>
+        <v>0.9773462783171522</v>
       </c>
       <c r="R23" t="n">
-        <v>0.003179650238473768</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0.1309328968903437</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5953125</v>
+        <v>0.009160305343511451</v>
       </c>
       <c r="V23" t="n">
-        <v>0.003081664098613251</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1305732484076433</v>
+        <v>0.65814696485623</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.9028213166144201</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.3427230046948357</v>
+        <v>0.1142384105960265</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.1070287539936102</v>
+        <v>0.5787728026533997</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1130573248407643</v>
+        <v>0.03605015673981191</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1145161290322581</v>
+        <v>0.9042386185243328</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.115919629057187</v>
+        <v>0.1580645161290322</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.1203125</v>
+        <v>0.831230283911672</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1158059467918623</v>
+        <v>0.9884678747940692</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1092307692307692</v>
+        <v>0.9834162520729685</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.6528662420382165</v>
+        <v>0.8125</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.119496855345912</v>
+        <v>0.2725779967159278</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.1227786752827141</v>
+        <v>0.9808</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.1006289308176101</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.3184615384615385</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.1329305135951662</v>
+        <v>0.02302631578947368</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.5288611544461779</v>
+        <v>0.01505016722408027</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.6374807987711214</v>
+        <v>0.07455429497568881</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.0679304897314376</v>
+        <v>0.05331179321486268</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.4618834080717489</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.1029185867895545</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.9952229299363057</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0.6977848101265823</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0.9859594383775351</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0.463884430176565</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0.08744038155802862</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0.5</v>
+        <v>0.5419354838709678</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5796875</v>
+        <v>0.342443729903537</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.3420195439739414</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5165876777251185</v>
+        <v>0.2108731466227348</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5445859872611465</v>
+        <v>0.006611570247933884</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.001675041876046901</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.3421487603305785</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9891640866873065</v>
+        <v>0.001636661211129296</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.4159869494290375</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9855769230769231</v>
+        <v>0.3185550082101806</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.3609271523178808</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.6366559485530546</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6129541864139021</v>
+        <v>0.09149277688603531</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9857142857142858</v>
+        <v>0.3824959481361426</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.875</v>
+        <v>0.6546644844517185</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.6336134453781512</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1456</v>
+        <v>0.4127243066884176</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4992050874403816</v>
+        <v>0.6523125996810207</v>
       </c>
       <c r="U24" t="n">
-        <v>0.478806907378336</v>
+        <v>0.3616692426584235</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.645933014354067</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1305732484076433</v>
+        <v>0.65814696485623</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2750397456279809</v>
+        <v>0.2213247172859451</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.7393364928909952</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.9869706840390879</v>
+        <v>0.6491525423728813</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.9853896103896104</v>
+        <v>0.3799682034976153</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.913961038961039</v>
+        <v>0.744</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.9845440494590417</v>
+        <v>0.4009584664536741</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.9843260188087775</v>
+        <v>0.7479935794542536</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.9889240506329114</v>
+        <v>0.6068515497553018</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.984472049689441</v>
+        <v>0.615257048092869</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.008038585209003215</v>
+        <v>0.7648953301127214</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.9821717990275527</v>
+        <v>0.4455284552845529</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.9983498349834984</v>
+        <v>0.7303921568627451</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.990521327014218</v>
+        <v>0.3145161290322581</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.7637795275590551</v>
+        <v>0.6672051696284329</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.9602446483180428</v>
+        <v>0.3544715447154472</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.5576619273301737</v>
+        <v>0.3226351351351351</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.006144393241167435</v>
+        <v>0.3941368078175896</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.8422712933753943</v>
+        <v>0.3563218390804598</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.001533742331288344</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0.9858267716535433</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.1790322580645161</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.1736334405144695</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0.01116427432216906</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0.08962264150943396</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0.617363344051447</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0.5682888540031397</v>
+        <v>0.826645264847512</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6835637480798771</v>
+        <v>0.5758064516129032</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.5314009661835749</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7268445839874411</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7169811320754716</v>
+        <v>0.3222591362126246</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01713395638629283</v>
+        <v>0.3560975609756097</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.6437908496732027</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2597597597597597</v>
+        <v>0.3425774877650897</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.6376811594202898</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.6310679611650486</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.6519607843137255</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7126984126984127</v>
+        <v>0.2852512155591572</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7507936507936508</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2453416149068323</v>
+        <v>0.4392220421393841</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.1046698872785829</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1411042944785276</v>
+        <v>0.004807692307692308</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9318541996830428</v>
+        <v>0.4730831973898858</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7543035993740219</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.6460587326120556</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9028213166144201</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2750397456279809</v>
+        <v>0.2213247172859451</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.5396578538102644</v>
+        <v>0.4856661045531197</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.2414355628058727</v>
+        <v>0.2111486486486487</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.695859872611465</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.03514376996805112</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.260061919504644</v>
+        <v>0.4297124600638977</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2621664050235479</v>
+        <v>0.07188498402555911</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.2662440570522979</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.2553516819571865</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.4725274725274725</v>
+        <v>0.09646302250803858</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.2527301092043682</v>
+        <v>0.504885993485342</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.2588996763754045</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.2327044025157233</v>
+        <v>0.8931419457735247</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.5077160493827161</v>
+        <v>0.255663430420712</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.2762762762762763</v>
+        <v>0.6442622950819672</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.7071651090342679</v>
+        <v>0.6503378378378378</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.4355828220858896</v>
+        <v>0.6254071661237784</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.1518987341772152</v>
+        <v>0.5308441558441559</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.275968992248062</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.2384615384615385</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.945859872611465</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.9352290679304898</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.8732394366197183</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0.6591639871382636</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.2283464566929134</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.6847826086956522</v>
+        <v>0.2418300653594771</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8790697674418605</v>
+        <v>0.8916666666666667</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9900332225913622</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8522012578616353</v>
+        <v>0.4906303236797274</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8665620094191523</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.7658119658119659</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7331288343558282</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.8094435075885329</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.0957983193277311</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8</v>
+        <v>0.02124183006535948</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7914012738853503</v>
+        <v>0.1254295532646048</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7203125</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.391156462585034</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5935085007727975</v>
+        <v>0.1531986531986532</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.1179487179487179</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4283387622149837</v>
+        <v>0.9966159052453468</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8362204724409449</v>
+        <v>0.116504854368932</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8306962025316456</v>
+        <v>0.7835218093699515</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.1191275167785235</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3427230046948357</v>
+        <v>0.1142384105960265</v>
       </c>
       <c r="X26" t="n">
-        <v>0.7393364928909952</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5396578538102644</v>
+        <v>0.4856661045531197</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.7346278317152104</v>
+        <v>0.5927209705372617</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.7419871794871795</v>
+        <v>0.7549342105263158</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6344605475040258</v>
+        <v>0.2370617696160267</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.735202492211838</v>
+        <v>0.9966722129783694</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.7310664605873262</v>
+        <v>0.3338870431893688</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.7531446540880503</v>
+        <v>0.1378151260504202</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.7303543913713405</v>
+        <v>0.1213675213675214</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.103448275862069</v>
+        <v>0.3607382550335571</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.7321711568938193</v>
+        <v>0.6189655172413793</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.734959349593496</v>
+        <v>0.1433389544688027</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.7208931419457735</v>
+        <v>0.731418918918919</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.9844961240310077</v>
+        <v>0.6537162162162162</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.75</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.8503086419753086</v>
+        <v>0.7783595113438045</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.09494640122511486</v>
+        <v>0.7520938023450586</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5764331210191083</v>
+        <v>0.9796610169491525</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.02111613876319759</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0.7071651090342679</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.4382022471910113</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.4529505582137161</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0.1211631663974152</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0.3426356589147287</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0.7151898734177216</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0.8732612055641422</v>
+        <v>0.5993265993265994</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5496794871794872</v>
+        <v>0.4151260504201681</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.5058823529411764</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4840255591054313</v>
+        <v>0.2033898305084746</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5149006622516556</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.3407534246575342</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.3506711409395973</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.3235800344234079</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.3446519524617996</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.5733558178752108</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5737704918032787</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="N27" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.5976027397260274</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.6183986371379898</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.8569023569023569</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.89171974522293</v>
+        <v>0.635</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1247947454844007</v>
+        <v>0.6520979020979021</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4724919093851133</v>
+        <v>0.5799676898222941</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4453376205787781</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.5793918918918919</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1070287539936102</v>
+        <v>0.5787728026533997</v>
       </c>
       <c r="X27" t="n">
-        <v>0.9869706840390879</v>
+        <v>0.6491525423728813</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2414355628058727</v>
+        <v>0.2111486486486487</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.7346278317152104</v>
+        <v>0.5927209705372617</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0.3522727272727273</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.9294117647058824</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>0.6398659966499163</v>
       </c>
       <c r="AE27" t="n">
-        <v>1</v>
+        <v>0.8130217028380634</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0.5963149078726968</v>
       </c>
       <c r="AG27" t="n">
-        <v>1</v>
+        <v>0.5989761092150171</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.008210180623973728</v>
+        <v>0.8612040133779264</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>0.3780068728522337</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0.6296928327645052</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
+        <v>0.3116666666666666</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.7552</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.9770290964777948</v>
+        <v>0.3533447684391081</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.3268551236749117</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.003194888178913738</v>
+        <v>0.3519458544839256</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.8592</v>
+        <v>0.5034364261168385</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.0046801872074883</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.1454849498327759</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.1517128874388254</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0.001644736842105263</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0.08025682182985554</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0.5917355371900826</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0.5475040257648953</v>
+        <v>0.7993197278911565</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5507936507936508</v>
+        <v>0.8801261829652997</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8006279434850864</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>0.6916932907348243</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5211726384364821</v>
+        <v>0.001612903225806452</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.02117263843648208</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.9373996789727127</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.02852614896988907</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.9354330708661417</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.9287974683544303</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.03993610223642172</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5888888888888889</v>
+        <v>0.021671826625387</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5048543689320388</v>
+        <v>0.03420195439739414</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.7131410256410257</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.2173228346456693</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8808373590982287</v>
+        <v>0.05520504731861198</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.0420032310177706</v>
       </c>
       <c r="S28" t="n">
-        <v>0.140983606557377</v>
+        <v>0.7364217252396166</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4856687898089172</v>
+        <v>0.04134762633996937</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4601910828025478</v>
+        <v>0.953030303030303</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.03616352201257862</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1130573248407643</v>
+        <v>0.03605015673981191</v>
       </c>
       <c r="X28" t="n">
-        <v>0.9853896103896104</v>
+        <v>0.3799682034976153</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.2592592592592592</v>
+        <v>0.695859872611465</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.7419871794871795</v>
+        <v>0.7549342105263158</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
+        <v>0.3522727272727273</v>
       </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.9279869067103109</v>
+        <v>0.109204368174727</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>0.6951026856240127</v>
       </c>
       <c r="AE28" t="n">
-        <v>1</v>
+        <v>0.1744548286604361</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>0.04724409448818898</v>
       </c>
       <c r="AG28" t="n">
-        <v>1</v>
+        <v>0.04784688995215311</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.008210180623973728</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>0.706645056726094</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1</v>
+        <v>0.04006410256410257</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0.9845679012345679</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.7601246105919003</v>
+        <v>0.4200626959247649</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.9722222222222222</v>
+        <v>0.9294871794871795</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.5464743589743589</v>
+        <v>0.9341021416803954</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.003134796238244514</v>
+        <v>0.887459807073955</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.8481012658227848</v>
+        <v>0.8328025477707006</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.004658385093167702</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.1581548599670511</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.1494435612082671</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0.003246753246753247</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0.07740916271721959</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0.5927152317880795</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0.5497630331753555</v>
+        <v>0.4572784810126582</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4621578099838969</v>
+        <v>0.09531249999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.1589825119236884</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4085850556438791</v>
+        <v>0.03833865814696485</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4267100977198697</v>
+        <v>0.01437699680511182</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001592356687898089</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.07049180327868852</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9229559748427673</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9189627228525121</v>
+        <v>0.05475040257648953</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.08103727714748785</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.1283676703645008</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4059900166389351</v>
+        <v>0.8967741935483871</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9234449760765551</v>
+        <v>0.2614896988906498</v>
       </c>
       <c r="P29" t="n">
-        <v>0.003294892915980231</v>
+        <v>0.9561815336463224</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9278846153846154</v>
+        <v>0.904</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.8926829268292683</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1185308848080134</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3938906752411576</v>
+        <v>0.891271056661562</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3608414239482201</v>
+        <v>0.07174887892376682</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.8952380952380953</v>
       </c>
       <c r="W29" t="n">
-        <v>0.1145161290322581</v>
+        <v>0.9042386185243328</v>
       </c>
       <c r="X29" t="n">
-        <v>0.913961038961039</v>
+        <v>0.744</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.03514376996805112</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.6344605475040258</v>
+        <v>0.2370617696160267</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.9294117647058824</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.9279869067103109</v>
+        <v>0.109204368174727</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.921875</v>
+        <v>0.2875399361022364</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.9212218649517685</v>
+        <v>0.9844961240310077</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.9235668789808917</v>
+        <v>0.8990384615384616</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.9511811023622048</v>
+        <v>0.9153094462540716</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.09238249594813615</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.9146141215106732</v>
+        <v>0.2915309446254072</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.9201331114808652</v>
+        <v>0.946031746031746</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.9356913183279743</v>
+        <v>0.06220095693779904</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.6719492868462758</v>
+        <v>0.6841269841269841</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.9116279069767442</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.4387096774193548</v>
+        <v>0.07213114754098361</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.0589171974522293</v>
+        <v>0.1277955271565495</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.9297385620915033</v>
+        <v>0.1502423263327948</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.08398133748055987</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.9403453689167975</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.1393034825870647</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.1352657004830918</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0.04462809917355372</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.08945686900958466</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.5008183306055647</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.9341021416803954</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0.456140350877193</v>
+        <v>0.645933014354067</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5541795665634675</v>
+        <v>0.8507223113964687</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.9483870967741935</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4930448222565688</v>
+        <v>0.4457236842105263</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5197472353870458</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.714759535655058</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.709470304975923</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.7655737704918033</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.7100494233937397</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.0211038961038961</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5023622047244094</v>
+        <v>0.1822742474916388</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.4228934817170111</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8755760368663594</v>
+        <v>0.2012882447665056</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.1616666666666667</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1291866028708134</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.4744976816074188</v>
+        <v>0.1669266770670827</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4468412942989214</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.1677316293929713</v>
       </c>
       <c r="W30" t="n">
-        <v>0.115919629057187</v>
+        <v>0.1580645161290322</v>
       </c>
       <c r="X30" t="n">
-        <v>0.9845440494590417</v>
+        <v>0.4009584664536741</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.260061919504644</v>
+        <v>0.4297124600638977</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.735202492211838</v>
+        <v>0.9966722129783694</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0.6398659966499163</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0.6951026856240127</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.921875</v>
+        <v>0.2875399361022364</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1</v>
+        <v>0.3769716088328076</v>
       </c>
       <c r="AF30" t="n">
-        <v>1</v>
+        <v>0.1890145395799677</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0.1688524590163935</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.006279434850863423</v>
+        <v>0.4054927302100161</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0.5836065573770491</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0.1968</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>0.6617647058823529</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.7674772036474165</v>
+        <v>0.6912</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.7431781701444623</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.5349922239502333</v>
+        <v>0.731418918918919</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.003048780487804878</v>
+        <v>0.7011308562197092</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.8395638629283489</v>
+        <v>0.943986820428336</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.004545454545454545</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.1561514195583596</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.1559055118110236</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0.001582278481012658</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0.08087091757387248</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0.5987261146496815</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0.5504587155963303</v>
+        <v>0.5771704180064309</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5536547433903577</v>
+        <v>0.1540930979133226</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.2512</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4921630094043887</v>
+        <v>0.06991869918699187</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5173501577287066</v>
+        <v>0.009584664536741214</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1284552845528455</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.1492776886035313</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.116504854368932</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.8128</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5841269841269842</v>
+        <v>0.1050955414012739</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5047318611987381</v>
+        <v>0.8377049180327869</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0.3549920760697306</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.9701726844583988</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8761609907120743</v>
+        <v>0.8194888178913738</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.8105436573311368</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1405492730210016</v>
+        <v>0.3414239482200647</v>
       </c>
       <c r="T31" t="n">
-        <v>0.478806907378336</v>
+        <v>0.8248062015503876</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4494556765163297</v>
+        <v>0.1305007587253414</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.8214849921011058</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1203125</v>
+        <v>0.831230283911672</v>
       </c>
       <c r="X31" t="n">
-        <v>0.9843260188087775</v>
+        <v>0.7479935794542536</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.2621664050235479</v>
+        <v>0.07188498402555911</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.7310664605873262</v>
+        <v>0.3338870431893688</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0.8130217028380634</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0.1744548286604361</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.9212218649517685</v>
+        <v>0.9844961240310077</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>0.3769716088328076</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>1</v>
+        <v>0.8208</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.9936708860759493</v>
       </c>
       <c r="AI31" t="n">
-        <v>1</v>
+        <v>0.3147540983606558</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1</v>
+        <v>0.8672985781990521</v>
       </c>
       <c r="AK31" t="n">
-        <v>1</v>
+        <v>0.1208791208791209</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.7634408602150538</v>
+        <v>0.7634920634920634</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.9758308157099698</v>
+        <v>0.1365079365079365</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.5397815912636506</v>
+        <v>0.1212624584717608</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.003062787136294028</v>
+        <v>0.1733547351524879</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.8393700787401575</v>
+        <v>0.2313915857605178</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.004511278195488722</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.1650793650793651</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.1619496855345912</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0.00315955766192733</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0.08668730650154799</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0.5901898734177216</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0.5560747663551402</v>
+        <v>0.6872037914691943</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5634674922600619</v>
+        <v>0.02131147540983606</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.08745874587458746</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5101404056162246</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5347758887171561</v>
+        <v>0.02302631578947368</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.001677852348993289</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.01487603305785124</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.00975609756097561</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.03074433656957929</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0.001658374792703151</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.01963993453355155</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.9884678747940692</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5984375</v>
+        <v>0.1578099838969404</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5164319248826291</v>
+        <v>0.9884105960264901</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0.1821138211382114</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.7688603531300161</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.8728682170542635</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.9916805324459235</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1376</v>
+        <v>0.1586776859504132</v>
       </c>
       <c r="T32" t="n">
-        <v>0.490625</v>
+        <v>0.9889589905362776</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4661538461538461</v>
+        <v>0.0046875</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.9934640522875817</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1158059467918623</v>
+        <v>0.9884678747940692</v>
       </c>
       <c r="X32" t="n">
-        <v>0.9889240506329114</v>
+        <v>0.6068515497553018</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.2662440570522979</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.7531446540880503</v>
+        <v>0.1378151260504202</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0.5963149078726968</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0.04724409448818898</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.9235668789808917</v>
+        <v>0.8990384615384616</v>
       </c>
       <c r="AD32" t="n">
-        <v>1</v>
+        <v>0.1890145395799677</v>
       </c>
       <c r="AE32" t="n">
-        <v>1</v>
+        <v>0.8208</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
@@ -5498,155 +4738,131 @@
         <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.007886435331230283</v>
+        <v>0.7898193760262726</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>0.2680921052631579</v>
       </c>
       <c r="AJ32" t="n">
         <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.7880184331797235</v>
+        <v>0.5261437908496732</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.9806259314456036</v>
+        <v>0.01954397394136808</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.5403726708074534</v>
+        <v>0.008561643835616438</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.00308641975308642</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.8391167192429022</v>
+        <v>0.06745362563237774</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.0045662100456621</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.1603174603174603</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0.1611374407582938</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0.003169572107765452</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0.07561728395061729</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0.6112</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0.5601217656012176</v>
+        <v>0.4925864909390445</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.546969696969697</v>
+        <v>0.02283849918433932</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.07467532467532467</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4818181818181818</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5054432348367029</v>
+        <v>0.01845637583892618</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.001689189189189189</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.01535836177474403</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.008223684210526315</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.03459637561779242</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0.003316749585406302</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.02635914332784185</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.9851973684210527</v>
       </c>
       <c r="M33" t="n">
-        <v>0.577639751552795</v>
+        <v>0.1631663974151858</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4984177215189873</v>
+        <v>0.9833055091819699</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0.1565074135090609</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.7974068071312804</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8931297709923665</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.984873949579832</v>
       </c>
       <c r="S33" t="n">
-        <v>0.126984126984127</v>
+        <v>0.1442786069651741</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4668721109399075</v>
+        <v>0.9841521394611727</v>
       </c>
       <c r="U33" t="n">
-        <v>0.434984520123839</v>
+        <v>0.00949367088607595</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.9887820512820513</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1092307692307692</v>
+        <v>0.9834162520729685</v>
       </c>
       <c r="X33" t="n">
-        <v>0.984472049689441</v>
+        <v>0.615257048092869</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.2553516819571865</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.7303543913713405</v>
+        <v>0.1213675213675214</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0.5989761092150171</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0.04784688995215311</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.9511811023622048</v>
+        <v>0.9153094462540716</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>0.1688524590163935</v>
       </c>
       <c r="AE33" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AF33" t="n">
         <v>1</v>
@@ -5655,469 +4871,397 @@
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.007739938080495356</v>
+        <v>0.8172757475083057</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>0.2715008431703204</v>
       </c>
       <c r="AJ33" t="n">
         <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
+        <v>0.001633986928104575</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.7630769230769231</v>
+        <v>0.5191986644407346</v>
       </c>
       <c r="AM33" t="n">
-        <v>1</v>
+        <v>0.02152317880794702</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.5254237288135594</v>
+        <v>0.01686340640809443</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.003012048192771084</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.8682170542635659</v>
+        <v>0.05218855218855219</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.004484304932735426</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.1511811023622047</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.1470588235294118</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0.00315955766192733</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0.0783132530120482</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0.5854430379746836</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0.5444947209653092</v>
+        <v>0.5074380165289256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1959564541213064</v>
+        <v>0.1893203883495146</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2088607594936709</v>
+        <v>0.2790322580645161</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2294573643410853</v>
+        <v>0.09461663947797716</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2110236220472441</v>
+        <v>0.006525285481239805</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3092621664050236</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.226537216828479</v>
+        <v>0.1523500810372772</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0060790273556231</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2062992125984252</v>
+        <v>0.1693290734824281</v>
       </c>
       <c r="J34" t="n">
-        <v>0.007898894154818325</v>
+        <v>0.1373182552504039</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2256493506493507</v>
+        <v>0.1650326797385621</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1984251968503937</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1752411575562701</v>
+        <v>0.1098726114649682</v>
       </c>
       <c r="N34" t="n">
-        <v>0.22508038585209</v>
+        <v>0.803921568627451</v>
       </c>
       <c r="O34" t="n">
-        <v>0.004694835680751174</v>
+        <v>0.3776337115072934</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2676056338028169</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1133858267716535</v>
+        <v>0.8066561014263075</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2122186495176849</v>
+        <v>0.7859531772575251</v>
       </c>
       <c r="S34" t="n">
-        <v>0.5957792207792207</v>
+        <v>0.3782894736842105</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2340764331210191</v>
+        <v>0.7996870109546166</v>
       </c>
       <c r="U34" t="n">
-        <v>0.23950233281493</v>
+        <v>0.1533742331288344</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2232558139534884</v>
+        <v>0.797427652733119</v>
       </c>
       <c r="W34" t="n">
-        <v>0.6528662420382165</v>
+        <v>0.8125</v>
       </c>
       <c r="X34" t="n">
-        <v>0.008038585209003215</v>
+        <v>0.7648953301127214</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.4725274725274725</v>
+        <v>0.09646302250803858</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.103448275862069</v>
+        <v>0.3607382550335571</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.008210180623973728</v>
+        <v>0.8612040133779264</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.008210180623973728</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.09238249594813615</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.006279434850863423</v>
+        <v>0.4054927302100161</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.9936708860759493</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.007886435331230283</v>
+        <v>0.7898193760262726</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.007739938080495356</v>
+        <v>0.8172757475083057</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.006289308176100629</v>
+        <v>0.3169129720853859</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.006535947712418301</v>
+        <v>0.8562197092084006</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.006309148264984227</v>
+        <v>0.1469648562300319</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.09233176838810642</v>
+        <v>0.8231511254019293</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.01060606060606061</v>
+        <v>0.1615508885298869</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.2234206471494607</v>
+        <v>0.1475409836065574</v>
       </c>
       <c r="AO34" t="n">
-        <v>1</v>
+        <v>0.1939586645468998</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.1596774193548387</v>
+        <v>0.2620232172470978</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.8923076923076924</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0.006201550387596899</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.5919354838709677</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.5476190476190477</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0.7071651090342679</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0.1658692185007974</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0.00644122383252818</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0.2006269592476489</v>
+        <v>0.7475728155339806</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5461658841940532</v>
+        <v>0.6841243862520459</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6270903010033445</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4889589905362776</v>
+        <v>0.5083612040133779</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5205696202531646</v>
+        <v>0.005</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.00684931506849315</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.7761437908496732</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0.7074380165289256</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.7651006711409396</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.2630718954248366</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.0593900481540931</v>
       </c>
       <c r="N35" t="n">
-        <v>0.5087719298245614</v>
+        <v>0.2716666666666667</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0.589018302828619</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.351575456053068</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.8757861635220126</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.2789915966386555</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1314935064935065</v>
+        <v>0.5896147403685092</v>
       </c>
       <c r="T35" t="n">
-        <v>0.4755905511811024</v>
+        <v>0.2736</v>
       </c>
       <c r="U35" t="n">
-        <v>0.4544025157232705</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.2615894039735099</v>
       </c>
       <c r="W35" t="n">
-        <v>0.119496855345912</v>
+        <v>0.2725779967159278</v>
       </c>
       <c r="X35" t="n">
-        <v>0.9821717990275527</v>
+        <v>0.4455284552845529</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2527301092043682</v>
+        <v>0.504885993485342</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.7321711568938193</v>
+        <v>0.6189655172413793</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0.3780068728522337</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0.706645056726094</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.9146141215106732</v>
+        <v>0.2915309446254072</v>
       </c>
       <c r="AD35" t="n">
-        <v>1</v>
+        <v>0.5836065573770491</v>
       </c>
       <c r="AE35" t="n">
-        <v>1</v>
+        <v>0.3147540983606558</v>
       </c>
       <c r="AF35" t="n">
-        <v>1</v>
+        <v>0.2680921052631579</v>
       </c>
       <c r="AG35" t="n">
-        <v>1</v>
+        <v>0.2715008431703204</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.006289308176100629</v>
+        <v>0.3169129720853859</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0.2845257903494177</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>0.6826446280991736</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.7597503900156006</v>
+        <v>0.4309484193011647</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.9801223241590215</v>
+        <v>0.7814569536423841</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.5381026438569206</v>
+        <v>0.7521367521367521</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.0015600624024961</v>
+        <v>0.986644407345576</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.8343848580441641</v>
+        <v>0.6408094435075885</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.004622496147919877</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.1553398058252427</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.1590551181102362</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0.003236245954692557</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0.08463949843260188</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0.5891980360065466</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0.5484375</v>
+        <v>0.4702970297029703</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5632911392405063</v>
+        <v>0.03179650238473768</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.08842443729903537</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4952380952380953</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.522508038585209</v>
+        <v>0.021630615640599</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.00165016501650165</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.02131147540983606</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0.006493506493506494</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.03583061889250815</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.03262642740619902</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.9802955665024631</v>
       </c>
       <c r="M36" t="n">
-        <v>0.593192868719611</v>
+        <v>0.1647819063004846</v>
       </c>
       <c r="N36" t="n">
-        <v>0.5111464968152867</v>
+        <v>0.9833887043189369</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0.180354267310789</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.8414239482200647</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8770226537216829</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>0.9849498327759197</v>
       </c>
       <c r="S36" t="n">
-        <v>0.1407766990291262</v>
+        <v>0.1639344262295082</v>
       </c>
       <c r="T36" t="n">
-        <v>0.4895666131621188</v>
+        <v>0.9811320754716981</v>
       </c>
       <c r="U36" t="n">
-        <v>0.4582677165354331</v>
+        <v>0.01246105919003115</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.9838969404186796</v>
       </c>
       <c r="W36" t="n">
-        <v>0.1227786752827141</v>
+        <v>0.9808</v>
       </c>
       <c r="X36" t="n">
-        <v>0.9983498349834984</v>
+        <v>0.7303921568627451</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.2588996763754045</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.734959349593496</v>
+        <v>0.1433389544688027</v>
       </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>0.6296928327645052</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0.04006410256410257</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.9201331114808652</v>
+        <v>0.946031746031746</v>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0.1968</v>
       </c>
       <c r="AE36" t="n">
-        <v>1</v>
+        <v>0.8672985781990521</v>
       </c>
       <c r="AF36" t="n">
         <v>1</v>
@@ -6126,2412 +5270,964 @@
         <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.006535947712418301</v>
+        <v>0.8562197092084006</v>
       </c>
       <c r="AI36" t="n">
-        <v>1</v>
+        <v>0.2845257903494177</v>
       </c>
       <c r="AJ36" t="n">
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.7719298245614035</v>
+        <v>0.5566343042071198</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.9797191887675507</v>
+        <v>0.03099510603588907</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.02006688963210702</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.003144654088050315</v>
+        <v>0.09135399673735727</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.8338709677419355</v>
+        <v>0.06578947368421052</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.003110419906687403</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0.1584967320261438</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0.1558441558441558</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0.001639344262295082</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0.07717041800643087</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0.5944170771756979</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0.5584</v>
+        <v>0.5886178861788618</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5273010920436817</v>
+        <v>0.8622366288492707</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.7915993537964459</v>
       </c>
       <c r="D37" t="n">
-        <v>0.482442748091603</v>
+        <v>0.8665594855305466</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5038520801232665</v>
+        <v>0.03119868637110016</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.07154471544715447</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.9237147595356551</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0.07085346215780998</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.9145161290322581</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0.9311475409836065</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.9118589743589743</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5739268680445151</v>
+        <v>0.03503184713375796</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4960998439937597</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0.6781045751633987</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.1626794258373206</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9003115264797508</v>
+        <v>0.006504065040650406</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1171749598715891</v>
+        <v>0.6941747572815534</v>
       </c>
       <c r="T37" t="n">
-        <v>0.4564183835182251</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.4303599374021909</v>
+        <v>0.9342507645259939</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.1006289308176101</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.990521327014218</v>
+        <v>0.3145161290322581</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.2327044025157233</v>
+        <v>0.8931419457735247</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.7208931419457735</v>
+        <v>0.731418918918919</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>0.3116666666666666</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0.9845679012345679</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.9356913183279743</v>
+        <v>0.06220095693779904</v>
       </c>
       <c r="AD37" t="n">
-        <v>1</v>
+        <v>0.6617647058823529</v>
       </c>
       <c r="AE37" t="n">
-        <v>1</v>
+        <v>0.1208791208791209</v>
       </c>
       <c r="AF37" t="n">
-        <v>1</v>
+        <v>0.001618122977346278</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0.001633986928104575</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.006309148264984227</v>
+        <v>0.1469648562300319</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0.6826446280991736</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.7511591962905718</v>
+        <v>0.3800322061191627</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.9728506787330317</v>
+        <v>0.9157212317666127</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.5156739811912225</v>
+        <v>0.9238410596026491</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.003053435114503817</v>
+        <v>0.8660130718954249</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.8630573248407644</v>
+        <v>0.8093645484949833</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.003048780487804878</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.1374407582938389</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.1364365971107544</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0.001577287066246057</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0.06832298136645963</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0.5651465798045603</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0.5295950155763239</v>
+        <v>0.3737864077669903</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8208269525267994</v>
+        <v>0.4790322580645161</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5668789808917197</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7921875</v>
+        <v>0.2508196721311475</v>
       </c>
       <c r="E38" t="n">
-        <v>0.785824345146379</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.3947797716150082</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7937219730941704</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.4084967320261438</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7515625</v>
+        <v>0.3944353518821604</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.4022617124394184</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.505654281098546</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7456828885400314</v>
+        <v>0.0593900481540931</v>
       </c>
       <c r="N38" t="n">
-        <v>0.7364341085271318</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7538940809968847</v>
+        <v>0.6699029126213593</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.8464</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6191950464396285</v>
+        <v>0.5756097560975609</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.4941763727121464</v>
       </c>
       <c r="S38" t="n">
-        <v>0.3909531502423264</v>
+        <v>0.7051282051282052</v>
       </c>
       <c r="T38" t="n">
-        <v>0.7695924764890282</v>
+        <v>0.5179407176287052</v>
       </c>
       <c r="U38" t="n">
-        <v>0.7565485362095532</v>
+        <v>0.4083204930662558</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.5143769968051118</v>
       </c>
       <c r="W38" t="n">
-        <v>0.3184615384615385</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="X38" t="n">
-        <v>0.7637795275590551</v>
+        <v>0.6672051696284329</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.5077160493827161</v>
+        <v>0.255663430420712</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.9844961240310077</v>
+        <v>0.6537162162162162</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.7552</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.7601246105919003</v>
+        <v>0.4200626959247649</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.6719492868462758</v>
+        <v>0.6841269841269841</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.7674772036474165</v>
+        <v>0.6912</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.7634408602150538</v>
+        <v>0.7634920634920634</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.7880184331797235</v>
+        <v>0.5261437908496732</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.7630769230769231</v>
+        <v>0.5191986644407346</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.09233176838810642</v>
+        <v>0.8231511254019293</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.7597503900156006</v>
+        <v>0.4309484193011647</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.7719298245614035</v>
+        <v>0.5566343042071198</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.7511591962905718</v>
+        <v>0.3800322061191627</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.7782738095238095</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.7987519500780031</v>
+        <v>0.3953098827470687</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.09063444108761329</v>
+        <v>0.4173486088379705</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.6033950617283951</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.02252252252252252</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.7343511450381679</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.3990536277602524</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.4169230769230769</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0.1121642969984202</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.3164362519201229</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0.9112519809825673</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.7410296411856474</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0.8113496932515337</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5799701046337817</v>
+        <v>0.9207119741100324</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.8516129032258064</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5030120481927711</v>
+        <v>0.6445182724252492</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5398496240601504</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.008361204013377926</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9779411764705882</v>
+        <v>0.008223684210526315</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.970873786407767</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9758308157099698</v>
+        <v>0.9656862745098039</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.02597402597402598</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6018376722817764</v>
+        <v>0.01116427432216906</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5251141552511416</v>
+        <v>0.02675585284280936</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9759398496240601</v>
+        <v>0.7577235772357723</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.1872964169381107</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.8649468892261002</v>
+        <v>0.03064516129032258</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>0.02030456852791878</v>
       </c>
       <c r="S39" t="n">
-        <v>0.15600624024961</v>
+        <v>0.7696078431372549</v>
       </c>
       <c r="T39" t="n">
-        <v>0.5037707390648567</v>
+        <v>0.02531645569620253</v>
       </c>
       <c r="U39" t="n">
-        <v>0.481371087928465</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.0207667731629393</v>
       </c>
       <c r="W39" t="n">
-        <v>0.1329305135951662</v>
+        <v>0.02302631578947368</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9602446483180428</v>
+        <v>0.3544715447154472</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.2762762762762763</v>
+        <v>0.6442622950819672</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.75</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.9770290964777948</v>
+        <v>0.3533447684391081</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9722222222222222</v>
+        <v>0.9294871794871795</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.9116279069767442</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.7431781701444623</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.9758308157099698</v>
+        <v>0.1365079365079365</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.9806259314456036</v>
+        <v>0.01954397394136808</v>
       </c>
       <c r="AG39" t="n">
-        <v>1</v>
+        <v>0.02152317880794702</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.01060606060606061</v>
+        <v>0.1615508885298869</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.9801223241590215</v>
+        <v>0.7814569536423841</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.9797191887675507</v>
+        <v>0.03099510603588907</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.9728506787330317</v>
+        <v>0.9157212317666127</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.7782738095238095</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.5572065378900446</v>
+        <v>1</v>
       </c>
       <c r="AO39" t="n">
-        <v>0.00741839762611276</v>
+        <v>0.9672131147540983</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.8252279635258358</v>
+        <v>0.8731466227347611</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.005865102639296188</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0.973568281938326</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.1803030303030303</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0.009287925696594427</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0.09759759759759759</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0.6207951070336392</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0.9725609756097561</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.4188311688311688</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9721362229102167</v>
+        <v>0.930976430976431</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.8462809917355372</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9875</v>
+        <v>0.6512820512820513</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9813084112149533</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.008710801393728223</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5468277945619335</v>
+        <v>0.008517887563884156</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.9697478991596639</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5203761755485894</v>
+        <v>0.9699499165275459</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.01712328767123288</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8785488958990536</v>
+        <v>0.009917355371900827</v>
       </c>
       <c r="N40" t="n">
-        <v>0.931637519872814</v>
+        <v>0.01727115716753022</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5162287480680062</v>
+        <v>0.7495854063018242</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.1644518272425249</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3946957878315133</v>
+        <v>0.01830282861896839</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.0155440414507772</v>
       </c>
       <c r="S40" t="n">
-        <v>0.617741935483871</v>
+        <v>0.757679180887372</v>
       </c>
       <c r="T40" t="n">
-        <v>0.9857594936708861</v>
+        <v>0.01470588235294118</v>
       </c>
       <c r="U40" t="n">
-        <v>0.9829192546583851</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.009819967266775777</v>
       </c>
       <c r="W40" t="n">
-        <v>0.5288611544461779</v>
+        <v>0.01505016722408027</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5576619273301737</v>
+        <v>0.3226351351351351</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.7071651090342679</v>
+        <v>0.6503378378378378</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.8503086419753086</v>
+        <v>0.7783595113438045</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.3268551236749117</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.5464743589743589</v>
+        <v>0.9341021416803954</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.4387096774193548</v>
+        <v>0.07213114754098361</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.5349922239502333</v>
+        <v>0.731418918918919</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5397815912636506</v>
+        <v>0.1212624584717608</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.5403726708074534</v>
+        <v>0.008561643835616438</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.5254237288135594</v>
+        <v>0.01686340640809443</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.2234206471494607</v>
+        <v>0.1475409836065574</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.5381026438569206</v>
+        <v>0.7521367521367521</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.02006688963210702</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.5156739811912225</v>
+        <v>0.9238410596026491</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.7987519500780031</v>
+        <v>0.3953098827470687</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.5572065378900446</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="n">
         <v>1</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.1914241960183767</v>
+        <v>0.9468267581475128</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.3649289099526066</v>
+        <v>0.8694158075601375</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.06636500754147813</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.5129770992366413</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.6368</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.6451104100946372</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0.2734627831715211</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0.5412130637636081</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0.9606299212598425</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.5197472353870458</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0.9719188767550702</v>
+        <v>0.4039735099337748</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1812688821752266</v>
+        <v>0.8717532467532467</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2419601837672282</v>
+        <v>0.7990196078431373</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2187981510015408</v>
+        <v>0.6254180602006689</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2067901234567901</v>
+        <v>0.001631321370309951</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3440366972477064</v>
+        <v>0.006666666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>0.271875</v>
+        <v>0.9481605351170569</v>
       </c>
       <c r="H41" t="n">
-        <v>0.002962962962962963</v>
+        <v>0.01140065146579805</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2469512195121951</v>
+        <v>0.9690048939641109</v>
       </c>
       <c r="J41" t="n">
-        <v>0.003110419906687403</v>
+        <v>0.9024793388429752</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2531055900621118</v>
+        <v>0.9490131578947368</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2386018237082067</v>
+        <v>0.07479674796747968</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1679506933744222</v>
+        <v>0.01607717041800643</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2186046511627907</v>
+        <v>0.08263069139966273</v>
       </c>
       <c r="O41" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.7198697068403909</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2993827160493827</v>
+        <v>0.2234910277324633</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.09021406727828746</v>
+        <v>0.08674304418985269</v>
       </c>
       <c r="R41" t="n">
-        <v>0.2453416149068323</v>
+        <v>0.07321131447587355</v>
       </c>
       <c r="S41" t="n">
-        <v>0.5625990491283677</v>
+        <v>0.7245901639344262</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2321981424148607</v>
+        <v>0.07448494453248812</v>
       </c>
       <c r="U41" t="n">
-        <v>0.2367223065250379</v>
+        <v>0.942457231726283</v>
       </c>
       <c r="V41" t="n">
-        <v>0.2564491654021244</v>
+        <v>0.07779578606158834</v>
       </c>
       <c r="W41" t="n">
-        <v>0.6374807987711214</v>
+        <v>0.07455429497568881</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006144393241167435</v>
+        <v>0.3941368078175896</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.4355828220858896</v>
+        <v>0.6254071661237784</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.09494640122511486</v>
+        <v>0.7520938023450586</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.003194888178913738</v>
+        <v>0.3519458544839256</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.003134796238244514</v>
+        <v>0.887459807073955</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.0589171974522293</v>
+        <v>0.1277955271565495</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.003048780487804878</v>
+        <v>0.7011308562197092</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.003062787136294028</v>
+        <v>0.1733547351524879</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.00308641975308642</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003012048192771084</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="AH41" t="n">
-        <v>1</v>
+        <v>0.1939586645468998</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.0015600624024961</v>
+        <v>0.986644407345576</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.003144654088050315</v>
+        <v>0.09135399673735727</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.003053435114503817</v>
+        <v>0.8660130718954249</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.09063444108761329</v>
+        <v>0.4173486088379705</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.00741839762611276</v>
+        <v>0.9672131147540983</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.1914241960183767</v>
+        <v>0.9468267581475128</v>
       </c>
       <c r="AO41" t="n">
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.1265432098765432</v>
+        <v>0.8207705192629816</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.922272047832586</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0.002976190476190476</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.56875</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.5185758513931888</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0.6759259259259259</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0.1581395348837209</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.001557632398753894</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0.1937984496124031</v>
+        <v>0.456953642384106</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4024960998439938</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.009433962264150943</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.344391785150079</v>
+        <v>0.5360134003350083</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3700159489633174</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01095461658841941</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0046875</v>
+        <v>0.8644628099173554</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8495440729483282</v>
+        <v>0.001658374792703151</v>
       </c>
       <c r="I42" t="n">
-        <v>0.004724409448818898</v>
+        <v>0.8441127694859039</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8486312399355878</v>
+        <v>0.9003378378378378</v>
       </c>
       <c r="K42" t="n">
-        <v>0.008</v>
+        <v>0.8647746243739566</v>
       </c>
       <c r="L42" t="n">
-        <v>0.00782472613458529</v>
+        <v>0.03908794788273615</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.004893964110929853</v>
       </c>
       <c r="N42" t="n">
-        <v>0.3574803149606299</v>
+        <v>0.05084745762711865</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8520249221183801</v>
+        <v>0.9618573797678275</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0208</v>
+        <v>0.2915980230642504</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0.0755336617405583</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003231017770597738</v>
+        <v>0.04599659284497445</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0707395498392283</v>
+        <v>0.9681742043551089</v>
       </c>
       <c r="T42" t="n">
-        <v>0.3191823899371069</v>
+        <v>0.04846526655896607</v>
       </c>
       <c r="U42" t="n">
-        <v>0.3150470219435736</v>
+        <v>0.878740157480315</v>
       </c>
       <c r="V42" t="n">
-        <v>0.004651162790697674</v>
+        <v>0.04942339373970346</v>
       </c>
       <c r="W42" t="n">
-        <v>0.0679304897314376</v>
+        <v>0.05331179321486268</v>
       </c>
       <c r="X42" t="n">
-        <v>0.8422712933753943</v>
+        <v>0.3563218390804598</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.1518987341772152</v>
+        <v>0.5308441558441559</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.5764331210191083</v>
+        <v>0.9796610169491525</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.8592</v>
+        <v>0.5034364261168385</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.8481012658227848</v>
+        <v>0.8328025477707006</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.9297385620915033</v>
+        <v>0.1502423263327948</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.8395638629283489</v>
+        <v>0.943986820428336</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.8393700787401575</v>
+        <v>0.2313915857605178</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.8391167192429022</v>
+        <v>0.06745362563237774</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.8682170542635659</v>
+        <v>0.05218855218855219</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.1596774193548387</v>
+        <v>0.2620232172470978</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.8343848580441641</v>
+        <v>0.6408094435075885</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.8338709677419355</v>
+        <v>0.06578947368421052</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.8630573248407644</v>
+        <v>0.8093645484949833</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.6033950617283951</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.8252279635258358</v>
+        <v>0.8731466227347611</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.3649289099526066</v>
+        <v>0.8694158075601375</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.1265432098765432</v>
+        <v>0.8207705192629816</v>
       </c>
       <c r="AP42" t="n">
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.1743119266055046</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.8680124223602484</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.07336523125996811</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0.06929133858267716</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0.08771929824561403</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0.06055900621118013</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0.4408427876823339</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0.8679549114331723</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0.3987635239567233</v>
+        <v>0.5335515548281505</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.4501607717041801</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4040561622464899</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="D43" t="n">
-        <v>0.07121212121212121</v>
+        <v>0.2406504065040651</v>
       </c>
       <c r="E43" t="n">
-        <v>0.06727828746177369</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5225903614457831</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4234930448222566</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="H43" t="n">
-        <v>0.002928257686676428</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4009146341463415</v>
+        <v>0.4500818330605565</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0045662100456621</v>
+        <v>0.3937397034596375</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3800623052959501</v>
+        <v>0.4274193548387097</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3816793893129771</v>
+        <v>0.5390879478827362</v>
       </c>
       <c r="M43" t="n">
-        <v>0.05513016845329249</v>
+        <v>0.07740916271721959</v>
       </c>
       <c r="N43" t="n">
-        <v>0.06955177743431221</v>
+        <v>0.5522388059701493</v>
       </c>
       <c r="O43" t="n">
-        <v>0.004497751124437781</v>
+        <v>0.5926517571884984</v>
       </c>
       <c r="P43" t="n">
-        <v>0.4837209302325581</v>
+        <v>0.7887096774193548</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1291793313069909</v>
+        <v>0.5829307568438004</v>
       </c>
       <c r="R43" t="n">
-        <v>0.4104938271604938</v>
+        <v>0.5082781456953642</v>
       </c>
       <c r="S43" t="n">
-        <v>0.391304347826087</v>
+        <v>0.5880398671096345</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0776255707762557</v>
+        <v>0.5293185419968305</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0791476407914764</v>
+        <v>0.4332298136645963</v>
       </c>
       <c r="V43" t="n">
-        <v>0.4170403587443946</v>
+        <v>0.5237315875613748</v>
       </c>
       <c r="W43" t="n">
-        <v>0.4618834080717489</v>
+        <v>0.5419354838709678</v>
       </c>
       <c r="X43" t="n">
-        <v>0.001533742331288344</v>
+        <v>0.826645264847512</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.275968992248062</v>
+        <v>0.2418300653594771</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.02111613876319759</v>
+        <v>0.5993265993265994</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.0046801872074883</v>
+        <v>0.7993197278911565</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.004658385093167702</v>
+        <v>0.4572784810126582</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.08398133748055987</v>
+        <v>0.645933014354067</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.004545454545454545</v>
+        <v>0.5771704180064309</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.004511278195488722</v>
+        <v>0.6872037914691943</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0045662100456621</v>
+        <v>0.4925864909390445</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.004484304932735426</v>
+        <v>0.5074380165289256</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.8923076923076924</v>
+        <v>0.7475728155339806</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.004622496147919877</v>
+        <v>0.4702970297029703</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.003110419906687403</v>
+        <v>0.5886178861788618</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.003048780487804878</v>
+        <v>0.3737864077669903</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.02252252252252252</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.005865102639296188</v>
+        <v>0.4188311688311688</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.06636500754147813</v>
+        <v>0.4039735099337748</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.922272047832586</v>
+        <v>0.456953642384106</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.1743119266055046</v>
+        <v>0.5335515548281505</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.004457652303120356</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.3775671406003159</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.367283950617284</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0.8502340093603744</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0.4764079147640791</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0.04107424960505529</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0.00463678516228748</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.05038167938931298</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.5276073619631901</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.463302752293578</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.4916030534351145</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.5595054095826894</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.4721362229102167</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.9041731066460588</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.1175523349436393</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0.4567901234567901</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.4296636085626911</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.1029185867895545</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.9858267716535433</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.2384615384615385</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.7071651090342679</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.9403453689167975</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.006201550387596899</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0.7343511450381679</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.973568281938326</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0.5129770992366413</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0.002976190476190476</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.8680124223602484</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.004457652303120356</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0.1453396524486572</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.1430793157076205</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0.003110419906687403</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0.0736196319018405</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0.560126582278481</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.5209302325581395</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.6037441497659907</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.6565977742448331</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.6483870967741936</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.04081632653061224</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.1640625</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.14170692431562</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.5784469096671949</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.6495176848874598</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.1489698890649762</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.001610305958132045</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.05405405405405406</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.6714743589743589</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.6915739268680445</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.1790322580645161</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0.945859872611465</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0.4382022471910113</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.1454849498327759</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0.1581548599670511</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.1393034825870647</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.1561514195583596</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0.1650793650793651</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.1603174603174603</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.1511811023622047</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.5919354838709677</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.1553398058252427</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.1584967320261438</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0.1374407582938389</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0.3990536277602524</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0.6368</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0.56875</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0.07336523125996811</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0.3775671406003159</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0.1453396524486572</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0.6434359805510534</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0.9669291338582677</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0.5763546798029556</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0.1347402597402597</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0.6070287539936102</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.6213292117465224</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.6537267080745341</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.6392405063291139</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.02773497688751926</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.1603053435114504</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.1403508771929824</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5921259842519685</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.6687797147385103</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0.1419656786271451</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.05817610062893082</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.9983870967741936</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0.6807511737089202</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.699685534591195</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.9952229299363057</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.1736334405144695</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0.9352290679304898</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0.4529505582137161</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.1517128874388254</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.1494435612082671</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.1352657004830918</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.1559055118110236</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.1619496855345912</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.1611374407582938</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.1470588235294118</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.5476190476190477</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0.1590551181102362</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.1558441558441558</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0.1364365971107544</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0.4169230769230769</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0.1803030303030303</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0.6451104100946372</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0.5185758513931888</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0.06929133858267716</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0.367283950617284</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0.1430793157076205</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0.6009538950715422</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0.9875389408099688</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0.5823817292006526</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0.1358609794628752</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0.6095679012345679</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.2339089481946625</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.2057877813504823</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.2795527156549521</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.2576489533011272</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.3023622047244094</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.2256</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.003076923076923077</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.2135007849293564</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.003225806451612903</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.2171052631578947</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.2188498402555911</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.2688</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.001584786053882726</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.2599681020733652</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.06847133757961783</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.2088091353996737</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.6351791530944625</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.2921348314606741</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.2952380952380952</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.2125984251968504</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.6977848101265823</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.01116427432216906</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0.5192307692307693</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0.1211631663974152</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.001644736842105263</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.003246753246753247</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.04462809917355372</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.001582278481012658</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.00315955766192733</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.003169572107765452</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.00315955766192733</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0.003236245954692557</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.001639344262295082</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0.001577287066246057</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0.1121642969984202</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.009287925696594427</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0.2734627831715211</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0.08771929824561403</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0.8502340093603744</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0.003110419906687403</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0.6434359805510534</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0.6009538950715422</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0.7546875</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0.1986863711001642</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0.001610305958132045</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0.2348242811501597</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.512937595129376</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.003144654088050315</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.5632716049382716</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.5383411580594679</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.04923076923076923</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.081203007518797</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.003091190108191654</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.06487341772151899</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.004777070063694267</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.001524390243902439</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.4758942457231726</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.5467289719626168</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.07526881720430108</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.01257861635220126</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.04482225656877898</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.003149606299212598</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.9765258215962441</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0.5887850467289719</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0.5990712074303406</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.00302571860816944</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.9859594383775351</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.08962264150943396</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0.8732394366197183</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.3426356589147287</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.08025682182985554</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.07740916271721959</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.08945686900958466</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.08087091757387248</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0.08668730650154799</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.07561728395061729</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.0783132530120482</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.7071651090342679</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.08463949843260188</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.07717041800643087</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0.06832298136645963</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0.3164362519201229</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0.09759759759759759</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0.5412130637636081</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0.6759259259259259</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.06055900621118013</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.4764079147640791</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0.0736196319018405</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0.9669291338582677</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0.9875389408099688</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0.7546875</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0.4731012658227848</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0.07075471698113207</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0.5038402457757296</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9779527559055118</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.5987558320373251</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.579454253611557</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.8944805194805194</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0.9216965742251223</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.5707547169811321</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0.4528</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0.9712918660287081</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.9682034976152624</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0.463884430176565</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0.617363344051447</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0.6591639871382636</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.5917355371900826</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0.5927152317880795</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0.5008183306055647</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.5987261146496815</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0.5901898734177216</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0.6112</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.5854430379746836</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.1658692185007974</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0.5891980360065466</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.5944170771756979</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0.5651465798045603</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0.9112519809825673</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0.6207951070336392</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0.9606299212598425</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0.1581395348837209</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.4408427876823339</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.04107424960505529</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0.560126582278481</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.5763546798029556</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.5823817292006526</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0.1986863711001642</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0.4731012658227848</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0.5739837398373984</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.5300632911392406</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.4673046251993621</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.5007849293563579</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.5629032258064516</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.4719101123595505</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0.903125</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.1201923076923077</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0.4578696343402226</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.4272151898734177</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0.08744038155802862</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0.2283464566929134</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0.7151898734177216</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0.9341021416803954</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0.00644122383252818</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0.7410296411856474</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.9725609756097561</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0.5197472353870458</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0.001557632398753894</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.8679549114331723</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.00463678516228748</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.1347402597402597</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.1358609794628752</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0.001610305958132045</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0.07075471698113207</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0.5739837398373984</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0.5266457680250783</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.9907834101382489</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.546969696969697</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.5337519623233909</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.8918495297805643</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.9365079365079365</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0.5349922239502333</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.4101382488479263</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.592948717948718</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.9861111111111112</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.9815100154083205</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0.5682888540031397</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0.6847826086956522</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0.8732612055641422</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.5475040257648953</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.5497630331753555</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.456140350877193</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.5504587155963303</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0.5560747663551402</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0.5601217656012176</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.5444947209653092</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.2006269592476489</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.5484375</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.5584</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0.5295950155763239</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0.8113496932515337</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.5729166666666666</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0.9719188767550702</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0.1937984496124031</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.3987635239567233</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.05038167938931298</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.5209302325581395</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.6070287539936102</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.6095679012345679</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0.2348242811501597</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.5038402457757296</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.5266457680250783</v>
-      </c>
-      <c r="AY51" t="n">
         <v>1</v>
       </c>
     </row>
